--- a/public/template_report_order.xlsx
+++ b/public/template_report_order.xlsx
@@ -84,7 +84,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>客户名称</t>
+  </si>
+  <si>
+    <t>客户电话</t>
+  </si>
   <si>
     <t>签单公司</t>
   </si>
@@ -98,7 +104,13 @@
     <t>签单收据</t>
   </si>
   <si>
+    <t>李先生</t>
+  </si>
+  <si>
     <t>南京公司</t>
+  </si>
+  <si>
+    <t>王先生</t>
   </si>
   <si>
     <t>广州公司</t>
@@ -1038,17 +1050,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="3"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="12.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19" style="1" customWidth="1"/>
-    <col min="4" max="4" width="36" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="17.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19" style="1" customWidth="1"/>
+    <col min="6" max="6" width="36" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1061,33 +1075,51 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" ht="137.25" spans="1:4">
+    <row r="2" ht="137.25" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2">
-        <v>45897</v>
-      </c>
-      <c r="C2" s="1">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1373639</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2">
+        <v>46108</v>
+      </c>
+      <c r="E2" s="1">
         <v>10000</v>
       </c>
-      <c r="D2" s="1" t="str">
+      <c r="F2" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_D4B09E91F8274A7FA8EF242DB10D13D5",1)</f>
         <v>=DISPIMG("ID_D4B09E91F8274A7FA8EF242DB10D13D5",1)</v>
       </c>
     </row>
-    <row r="3" ht="157.5" spans="1:4">
+    <row r="3" ht="157.5" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2">
-        <v>45891</v>
-      </c>
-      <c r="C3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1896365</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2">
+        <v>45744</v>
+      </c>
+      <c r="E3" s="1">
         <v>20000</v>
       </c>
-      <c r="D3" s="1" t="str">
+      <c r="F3" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_17A0DD63C80C4DEAB0143EA79AE861AB",1)</f>
         <v>=DISPIMG("ID_17A0DD63C80C4DEAB0143EA79AE861AB",1)</v>
       </c>
